--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1464" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A22C68-DCD7-4A0F-816D-D05C7D542D43}"/>
+  <xr:revisionPtr revIDLastSave="1470" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E417EF-D020-4790-BFB5-433DAC0D9FF4}"/>
   <bookViews>
-    <workbookView xWindow="14028" yWindow="2052" windowWidth="8904" windowHeight="10116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9120" yWindow="1248" windowWidth="8844" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -147,6 +147,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3339,7 +3343,7 @@
         <v>-1067000</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>0</v>
       </c>
@@ -3349,8 +3353,11 @@
       <c r="C193" s="4">
         <v>46021</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D193" s="4">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,8 +3367,11 @@
       <c r="C194" s="6">
         <v>-948000</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D194" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>2</v>
       </c>
@@ -3371,8 +3381,11 @@
       <c r="C195" s="7">
         <v>403000</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D195" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>1</v>
       </c>
@@ -3382,8 +3395,11 @@
       <c r="C196" s="6">
         <v>516000</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D196" s="6">
+        <v>71000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>4</v>
       </c>
@@ -3394,6 +3410,10 @@
       <c r="C197" s="8">
         <f>C194+C195-C196</f>
         <v>-1061000</v>
+      </c>
+      <c r="D197" s="8">
+        <f>D194+D195-D196</f>
+        <v>-71000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1470" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E417EF-D020-4790-BFB5-433DAC0D9FF4}"/>
+  <xr:revisionPtr revIDLastSave="1476" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE5BF51C-8383-40E7-A0B2-197EC4DC373F}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="1248" windowWidth="8844" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14364" yWindow="1356" windowWidth="8676" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -3343,7 +3343,7 @@
         <v>-1067000</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>0</v>
       </c>
@@ -3356,8 +3356,11 @@
       <c r="D193" s="4">
         <v>46080</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E193" s="4">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>3</v>
       </c>
@@ -3370,8 +3373,11 @@
       <c r="D194" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E194" s="6">
+        <v>-315000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>2</v>
       </c>
@@ -3384,8 +3390,11 @@
       <c r="D195" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E195" s="7">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>1</v>
       </c>
@@ -3398,8 +3407,11 @@
       <c r="D196" s="6">
         <v>71000</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E196" s="6">
+        <v>90760</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>4</v>
       </c>
@@ -3414,6 +3426,10 @@
       <c r="D197" s="8">
         <f>D194+D195-D196</f>
         <v>-71000</v>
+      </c>
+      <c r="E197" s="8">
+        <f>E194+E195-E196</f>
+        <v>-333760</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1476" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE5BF51C-8383-40E7-A0B2-197EC4DC373F}"/>
+  <xr:revisionPtr revIDLastSave="1482" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D3757DD-2FFC-4FF5-BF99-C689AC1DF7D7}"/>
   <bookViews>
-    <workbookView xWindow="14364" yWindow="1356" windowWidth="8676" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14436" yWindow="1104" windowWidth="8604" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="5">
   <si>
     <t>Date</t>
   </si>
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -3432,6 +3432,47 @@
         <v>-333760</v>
       </c>
     </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B199" s="4">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B200" s="6">
+        <v>-315000</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B201" s="7">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B202" s="6">
+        <v>124000</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B203" s="8">
+        <f>B200+B201-B202</f>
+        <v>-355000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1482" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D3757DD-2FFC-4FF5-BF99-C689AC1DF7D7}"/>
+  <xr:revisionPtr revIDLastSave="1491" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A25622-E88B-4B2D-A621-E6228C01A024}"/>
   <bookViews>
-    <workbookView xWindow="14436" yWindow="1104" windowWidth="8604" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12408" yWindow="1404" windowWidth="10548" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -3439,6 +3439,12 @@
       <c r="B199" s="4">
         <v>46142</v>
       </c>
+      <c r="C199" s="4">
+        <v>46171</v>
+      </c>
+      <c r="D199" s="4">
+        <v>46203</v>
+      </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
@@ -3447,6 +3453,12 @@
       <c r="B200" s="6">
         <v>-315000</v>
       </c>
+      <c r="C200" s="6">
+        <v>-316000</v>
+      </c>
+      <c r="D200" s="6">
+        <v>-316000</v>
+      </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
@@ -3455,6 +3467,12 @@
       <c r="B201" s="7">
         <v>84000</v>
       </c>
+      <c r="C201" s="7">
+        <v>221000</v>
+      </c>
+      <c r="D201" s="7">
+        <v>271000</v>
+      </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
@@ -3463,6 +3481,12 @@
       <c r="B202" s="6">
         <v>124000</v>
       </c>
+      <c r="C202" s="6">
+        <v>170000</v>
+      </c>
+      <c r="D202" s="6">
+        <v>184000</v>
+      </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
@@ -3471,6 +3495,14 @@
       <c r="B203" s="8">
         <f>B200+B201-B202</f>
         <v>-355000</v>
+      </c>
+      <c r="C203" s="8">
+        <f>C200+C201-C202</f>
+        <v>-265000</v>
+      </c>
+      <c r="D203" s="8">
+        <f>D200+D201-D202</f>
+        <v>-229000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1491" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5A25622-E88B-4B2D-A621-E6228C01A024}"/>
+  <xr:revisionPtr revIDLastSave="1495" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18AD047D-2409-4AAF-B519-D7232AE394C2}"/>
   <bookViews>
-    <workbookView xWindow="12408" yWindow="1404" windowWidth="10548" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13776" yWindow="720" windowWidth="8964" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -147,10 +147,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3445,6 +3441,9 @@
       <c r="D199" s="4">
         <v>46203</v>
       </c>
+      <c r="E199" s="4">
+        <v>46234</v>
+      </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
@@ -3459,6 +3458,9 @@
       <c r="D200" s="6">
         <v>-316000</v>
       </c>
+      <c r="E200" s="6">
+        <v>-316000</v>
+      </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
@@ -3473,6 +3475,9 @@
       <c r="D201" s="7">
         <v>271000</v>
       </c>
+      <c r="E201" s="7">
+        <v>273000</v>
+      </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
@@ -3487,6 +3492,9 @@
       <c r="D202" s="6">
         <v>184000</v>
       </c>
+      <c r="E202" s="6">
+        <v>219000</v>
+      </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
@@ -3503,6 +3511,10 @@
       <c r="D203" s="8">
         <f>D200+D201-D202</f>
         <v>-229000</v>
+      </c>
+      <c r="E203" s="8">
+        <f>E200+E201-E202</f>
+        <v>-262000</v>
       </c>
     </row>
   </sheetData>
